--- a/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_gt_report.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M06_AU10</t>
+          <t>CF_M06_AU11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
+          <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,185 +500,185 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M06_AU08, CF_M06_AU07</t>
+          <t>CF_M06_AU09, CF_M06_AU07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>action, store</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Dispatcher</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The central axis that manages the entire data flow and notifies Stores when the state needs to be modified.</t>
+          <t>The Dispatcher notifies Stores when the state should be modified.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.731</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M06_AU11</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>CF_M06_AU12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>47</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M06_AU09, CF_M06_AU07</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>A Javascript object that indicates an intention to modify the application state.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M06_AU12</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>CF_M06_AU13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+          <t>Presentation: This is the layer that communicates with the user</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M06_AU03, CF_M06_AU12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>presentation, user</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>The layer that communicates with the user, displaying system data and collecting user input; in this case, the mobile application.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7607</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M06_AU13</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>CF_M06_AU14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Presentation: This is the layer that communicates with the user</t>
+          <t>is a library for building user interfaces using Javascript.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M06_AU03, CF_M06_AU12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>presentation, user</t>
-        </is>
-      </c>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The layer that communicates with the user, displaying system data and collecting user input; in this case, the mobile application.</t>
+          <t>A Javascript object that indicates an intention to modify the application state.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8952</v>
+        <v>0.7302999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M06_AU16</t>
+          <t>CF_M06_AU15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jest</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+          <t>is an open source framework for native Android, iOS and Web applications.</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -717,18 +717,18 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6788</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M06_AU17</t>
+          <t>CF_M06_AU16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NodeJS</t>
+          <t>Jest</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -738,43 +738,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
+          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>51</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>A Javascript object that indicates an intention to modify the application state.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.679</v>
+        <v>0.6788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M06_AU18</t>
+          <t>CF_M06_AU17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>NodeJS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -784,7 +788,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>it is a programming language developed and maintained by Microsoft</t>
+          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -805,22 +809,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>Development framework used to build the mobile application.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.6611</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M06_AU19</t>
+          <t>CF_M06_AU18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -830,7 +834,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
+          <t>it is a programming language developed and maintained by Microsoft</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -851,154 +855,150 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>Development framework used to build the mobile application.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6944</v>
+        <v>0.6611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mobile Application</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The project “Development of a mobile application for a digital signage company”</t>
+          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>Development framework used to build the mobile application.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.8665</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M06_AU24</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Mobile Application</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
-content. </t>
+          <t>The project “Development of a mobile application for a digital signage company”</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Mobile Device</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>The physical device where the application is hosted, either iOS or Android.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.7835</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M06_AU25</t>
+          <t>CF_M06_AU24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
+          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
+content. </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Library for building user interfaces using Javascript.</t>
+          <t>A Javascript object that indicates an intention to modify the application state.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.7194</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
+          <t>Communication protocol used between the mobile application and the Waapiti API.</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1085,17 +1085,21 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WebSocket</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Aquesta funcionalitat es connecta viasocket amb el servidor i mostra el contingut segons els missatges que aquest envia.</t>
+          <t>Communication protocol used for real-time logs and preview.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.6798</v>
+        <v>0.7111</v>
       </c>
     </row>
   </sheetData>
